--- a/output/pdf_financials_xlsx/MT.xlsx
+++ b/output/pdf_financials_xlsx/MT.xlsx
@@ -4477,40 +4477,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.504865</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.459433</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.49723</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.639992</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.468526</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.586857</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.7621019999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.7621019999999999</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="93">
@@ -5580,7 +5580,7 @@
         <v>0.007501</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.9</v>
+        <v>1.126216</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0.299</v>
@@ -7276,7 +7276,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>1.46</v>
       </c>
@@ -8452,7 +8456,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -14252,7 +14260,11 @@
           <t>Proceeds from recovery of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MT.xlsx
+++ b/output/pdf_financials_xlsx/MT.xlsx
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000471</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001411</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001203</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000915</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000358</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0.001398</v>
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-29.299994</v>
+        <v>-29.301345</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.536207</v>
+        <v>-0.536237</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.085838</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.762754</v>
+        <v>-1.763225</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.178227</v>
+        <v>-3.179638</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.556812</v>
+        <v>-2.558015</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.725577</v>
@@ -1618,10 +1618,10 @@
         <v>-2.153705</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.084884</v>
+        <v>0.083969</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.274146</v>
+        <v>-1.274504</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>0.101063</v>
@@ -1680,22 +1680,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-29.199521</v>
+        <v>-29.200872</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.460982</v>
+        <v>-0.461012</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.074984</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.755073</v>
+        <v>-1.755544</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.172746</v>
+        <v>-3.174157</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.552314</v>
+        <v>-2.553517</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.72192</v>
@@ -1704,10 +1704,10 @@
         <v>-2.151274</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.087076</v>
+        <v>0.086161</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.272117</v>
+        <v>-1.272475</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>0.102291</v>
@@ -1907,40 +1907,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.115297</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.301836</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.171821</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.61734</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.055114</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.150893</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.07982300000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.124568</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.770463</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.698825</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.219979</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.07521700000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1993,40 +1993,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.115297</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.301836</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.171821</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.61734</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.055114</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.150893</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.07982300000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.21056</v>
+        <v>0.335128</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.5073</v>
+        <v>1.277763</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.42998</v>
+        <v>1.128805</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.003222</v>
+        <v>1.223201</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.846884</v>
+        <v>0.9221009999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2509,40 +2509,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.19013</v>
+        <v>0.074833</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.304069</v>
+        <v>0.002233</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.177674</v>
+        <v>0.005853</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.614738</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.201638</v>
+        <v>0.146524</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.340076</v>
+        <v>0.189183</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.096998</v>
+        <v>0.017175</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.636163</v>
+        <v>0.511595</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.789035</v>
+        <v>0.018572</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.813487</v>
+        <v>0.114662</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.260511</v>
+        <v>0.040532</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.084457</v>
+        <v>0.00924</v>
       </c>
     </row>
     <row r="49">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">

--- a/output/pdf_financials_xlsx/MT.xlsx
+++ b/output/pdf_financials_xlsx/MT.xlsx
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.2637</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -23380,7 +23380,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -23606,7 +23610,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MT.xlsx
+++ b/output/pdf_financials_xlsx/MT.xlsx
@@ -694,22 +694,22 @@
         <v>0.700498</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.127843</v>
+        <v>0.422993</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.188889</v>
+        <v>0.520346</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.09241000000000001</v>
+        <v>0.368986</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.120327</v>
+        <v>0.670313</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.140037</v>
+        <v>0.597756</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.093653</v>
+        <v>0.383477</v>
       </c>
     </row>
     <row r="8">
@@ -3227,34 +3227,34 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.32986</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.263713</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.571257</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.007637</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.102661</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.148157</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.322962</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.014405</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.005793</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.007312</v>
       </c>
     </row>
     <row r="65">
@@ -3356,34 +3356,34 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.088126</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.09105000000000001</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.09105000000000001</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.09354999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.09354999999999999</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.09414400000000001</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.0982</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="68">
@@ -4840,16 +4840,16 @@
         <v>0.005724</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.015202</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.025435</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.006818</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001694</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0.001359</v>
@@ -4858,10 +4858,10 @@
         <v>-0.000593</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-8e-06</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.00144</v>
       </c>
     </row>
     <row r="102">
@@ -5457,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.018715</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.273754</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.417924</v>
       </c>
     </row>
     <row r="116">
@@ -9858,7 +9858,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -10386,7 +10390,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12150,7 +12158,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -12302,7 +12314,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17402,7 +17418,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -17776,7 +17796,11 @@
           <t>Value of warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -17850,7 +17874,11 @@
           <t>Value of finders’ warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -17998,7 +18026,11 @@
           <t>Shares issued in private placement 3,011,118 1,736,253 803,299</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -18760,7 +18792,11 @@
           <t>Shares issued in private placement 19,000,000 1,068,699 831,301</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -19366,7 +19402,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -20272,7 +20312,11 @@
           <t>Shares issued in private placement 19,940,420 1,795,874 628,521</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -20956,7 +21000,11 @@
           <t>Shares issued in private placement 30,111,177 1,736,253 803,299</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -22176,7 +22224,11 @@
           <t>Value of warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -22320,7 +22372,11 @@
           <t>Shares issued in private placement 10,000,000 426,720 173,280</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -22776,7 +22832,11 @@
           <t>Shares issued in private placement 20,415,420 1,852,874 644,861</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -24528,7 +24588,11 @@
           <t>Shares issued in private placement 1,000,000 29,948 20,052</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E246" s="5" t="n">
         <v>0.05</v>
       </c>
@@ -24988,7 +25052,11 @@
           <t>Consulting and directors fees (Note 9)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -28020,7 +28088,11 @@
           <t>Consulting and directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
